--- a/docs/이동수업_현황_보강양식_2026-2샘플.xlsx
+++ b/docs/이동수업_현황_보강양식_2026-2샘플.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:B7"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -407,43 +407,42 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>한 줄 = 함께 움직이는 한 묶음. 반 번호를 쉼표로, 각 반에 개설된 과목을 같은 순서로 적습니다.</v>
+        <v>한 줄 = 함께 움직이는 한 묶음. 「반=과목」 쌍을 쉼표로 나란히 적습니다. 순서는 상관없습니다.</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>반이 하나뿐인 줄 = 그 반만 듣는 단독 수업입니다. 단독도 꼭 적어 주세요 — 이 표에 없는 반의 배정은 오기재로 판정됩니다.</v>
+        <v>쌍이 하나뿐인 줄 = 그 반만 듣는 단독 수업입니다. 단독도 꼭 적어 주세요 —</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>예:  2 | 1, 6, 10 | 중국어회화, 인공지능기초, 기하     /     2 | 9 | 인공지능기초</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
+        <v>이 표에 없는 반의 배정은 오기재로 판정됩니다. 특별실은 이 표에 적지 않습니다(별도 관리).</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>예:  2 | 1=중국어회화, 6=인공지능기초, 10=기하     /     2 | 9=인공지능기초</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
         <v>학년</v>
       </c>
-      <c r="B6" t="str">
-        <v>반</v>
-      </c>
-      <c r="C6" t="str">
-        <v>과목 (반 순서대로)</v>
-      </c>
-      <c r="D6" t="str">
-        <v>특별실 (선택, 반 순서대로)</v>
+      <c r="B7" t="str">
+        <v>묶음 (반=과목 쌍을 쉼표로)</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D6"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B7"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D36"/>
+  <dimension ref="A1:B36"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -460,13 +459,7 @@
         <v>학년</v>
       </c>
       <c r="B4" t="str">
-        <v>반</v>
-      </c>
-      <c r="C4" t="str">
-        <v>과목 (반 순서대로)</v>
-      </c>
-      <c r="D4" t="str">
-        <v>특별실 (선택, 반 순서대로)</v>
+        <v>묶음 (반=과목 쌍을 쉼표로)</v>
       </c>
     </row>
     <row r="5">
@@ -474,13 +467,7 @@
         <v>2</v>
       </c>
       <c r="B5" t="str">
-        <v>1, 6, 10</v>
-      </c>
-      <c r="C5" t="str">
-        <v>중국어회화, 인공지능기초, 기하</v>
-      </c>
-      <c r="D5" t="str">
-        <v>-, 정보실 전 시수, -</v>
+        <v>1=중국어회화, 6=인공지능기초, 10=기하</v>
       </c>
     </row>
     <row r="6">
@@ -488,13 +475,7 @@
         <v>2</v>
       </c>
       <c r="B6" t="str">
-        <v>10</v>
-      </c>
-      <c r="C6" t="str">
-        <v>전자기와양자</v>
-      </c>
-      <c r="D6" t="str">
-        <v/>
+        <v>10=전자기와양자</v>
       </c>
     </row>
     <row r="7">
@@ -502,13 +483,7 @@
         <v>2</v>
       </c>
       <c r="B7" t="str">
-        <v>2, 3</v>
-      </c>
-      <c r="C7" t="str">
-        <v>일본어회화, 중국어회화</v>
-      </c>
-      <c r="D7" t="str">
-        <v/>
+        <v>2=일본어회화, 3=중국어회화</v>
       </c>
     </row>
     <row r="8">
@@ -516,13 +491,7 @@
         <v>2</v>
       </c>
       <c r="B8" t="str">
-        <v>4, 5, 7, 8</v>
-      </c>
-      <c r="C8" t="str">
-        <v>일본어회화, 중국어회화, 기하, 인공지능기초</v>
-      </c>
-      <c r="D8" t="str">
-        <v>-, -, -, 정보실 전 시수</v>
+        <v>4=일본어회화, 5=중국어회화, 7=기하, 8=인공지능기초</v>
       </c>
     </row>
     <row r="9">
@@ -530,13 +499,7 @@
         <v>2</v>
       </c>
       <c r="B9" t="str">
-        <v>6</v>
-      </c>
-      <c r="C9" t="str">
-        <v>전자기와양자</v>
-      </c>
-      <c r="D9" t="str">
-        <v/>
+        <v>6=전자기와양자</v>
       </c>
     </row>
     <row r="10">
@@ -544,13 +507,7 @@
         <v>2</v>
       </c>
       <c r="B10" t="str">
-        <v>6, 10</v>
-      </c>
-      <c r="C10" t="str">
-        <v>지구시스템과학, 세포와물질대사</v>
-      </c>
-      <c r="D10" t="str">
-        <v/>
+        <v>6=지구시스템과학, 10=세포와물질대사</v>
       </c>
     </row>
     <row r="11">
@@ -558,13 +515,7 @@
         <v>2</v>
       </c>
       <c r="B11" t="str">
-        <v>7</v>
-      </c>
-      <c r="C11" t="str">
-        <v>전자기와양자</v>
-      </c>
-      <c r="D11" t="str">
-        <v/>
+        <v>7=전자기와양자</v>
       </c>
     </row>
     <row r="12">
@@ -572,13 +523,7 @@
         <v>2</v>
       </c>
       <c r="B12" t="str">
-        <v>7</v>
-      </c>
-      <c r="C12" t="str">
-        <v>지구시스템과학</v>
-      </c>
-      <c r="D12" t="str">
-        <v/>
+        <v>7=지구시스템과학</v>
       </c>
     </row>
     <row r="13">
@@ -586,13 +531,7 @@
         <v>2</v>
       </c>
       <c r="B13" t="str">
-        <v>8</v>
-      </c>
-      <c r="C13" t="str">
-        <v>세포와물질대사</v>
-      </c>
-      <c r="D13" t="str">
-        <v/>
+        <v>8=세포와물질대사</v>
       </c>
     </row>
     <row r="14">
@@ -600,13 +539,7 @@
         <v>2</v>
       </c>
       <c r="B14" t="str">
-        <v>8, 9</v>
-      </c>
-      <c r="C14" t="str">
-        <v>전자기와양자, 지구시스템과학</v>
-      </c>
-      <c r="D14" t="str">
-        <v>-, 생명과학실 전 시수</v>
+        <v>8=전자기와양자, 9=지구시스템과학</v>
       </c>
     </row>
     <row r="15">
@@ -614,13 +547,7 @@
         <v>2</v>
       </c>
       <c r="B15" t="str">
-        <v>9</v>
-      </c>
-      <c r="C15" t="str">
-        <v>세포와물질대사</v>
-      </c>
-      <c r="D15" t="str">
-        <v/>
+        <v>9=세포와물질대사</v>
       </c>
     </row>
     <row r="16">
@@ -628,13 +555,7 @@
         <v>2</v>
       </c>
       <c r="B16" t="str">
-        <v>9</v>
-      </c>
-      <c r="C16" t="str">
-        <v>인공지능기초</v>
-      </c>
-      <c r="D16" t="str">
-        <v>정보실 전 시수</v>
+        <v>9=인공지능기초</v>
       </c>
     </row>
     <row r="17">
@@ -642,13 +563,7 @@
         <v>3</v>
       </c>
       <c r="B17" t="str">
-        <v>1, 1, 7</v>
-      </c>
-      <c r="C17" t="str">
-        <v>수학과제탐구, 수학과제탐구, 논술</v>
-      </c>
-      <c r="D17" t="str">
-        <v/>
+        <v>1=수학과제탐구, 1=수학과제탐구, 7=논술</v>
       </c>
     </row>
     <row r="18">
@@ -656,13 +571,7 @@
         <v>3</v>
       </c>
       <c r="B18" t="str">
-        <v>1, 3, 8</v>
-      </c>
-      <c r="C18" t="str">
-        <v>중국문화, 일본문화, 인공지능기초</v>
-      </c>
-      <c r="D18" t="str">
-        <v>-, -, 정보실 전 시수</v>
+        <v>1=중국문화, 3=일본문화, 8=인공지능기초</v>
       </c>
     </row>
     <row r="19">
@@ -670,13 +579,7 @@
         <v>3</v>
       </c>
       <c r="B19" t="str">
-        <v>10</v>
-      </c>
-      <c r="C19" t="str">
-        <v>논술</v>
-      </c>
-      <c r="D19" t="str">
-        <v/>
+        <v>10=논술</v>
       </c>
     </row>
     <row r="20">
@@ -684,13 +587,7 @@
         <v>3</v>
       </c>
       <c r="B20" t="str">
-        <v>10</v>
-      </c>
-      <c r="C20" t="str">
-        <v>인공지능기초</v>
-      </c>
-      <c r="D20" t="str">
-        <v>정보실 전 시수</v>
+        <v>10=인공지능기초</v>
       </c>
     </row>
     <row r="21">
@@ -698,13 +595,7 @@
         <v>3</v>
       </c>
       <c r="B21" t="str">
-        <v>10</v>
-      </c>
-      <c r="C21" t="str">
-        <v>화학Ⅱ</v>
-      </c>
-      <c r="D21" t="str">
-        <v/>
+        <v>10=화학Ⅱ</v>
       </c>
     </row>
     <row r="22">
@@ -712,13 +603,7 @@
         <v>3</v>
       </c>
       <c r="B22" t="str">
-        <v>2</v>
-      </c>
-      <c r="C22" t="str">
-        <v>중국문화</v>
-      </c>
-      <c r="D22" t="str">
-        <v/>
+        <v>2=중국문화</v>
       </c>
     </row>
     <row r="23">
@@ -726,13 +611,7 @@
         <v>3</v>
       </c>
       <c r="B23" t="str">
-        <v>3</v>
-      </c>
-      <c r="C23" t="str">
-        <v>논술</v>
-      </c>
-      <c r="D23" t="str">
-        <v/>
+        <v>3=논술</v>
       </c>
     </row>
     <row r="24">
@@ -740,13 +619,7 @@
         <v>3</v>
       </c>
       <c r="B24" t="str">
-        <v>4</v>
-      </c>
-      <c r="C24" t="str">
-        <v>논술</v>
-      </c>
-      <c r="D24" t="str">
-        <v/>
+        <v>4=논술</v>
       </c>
     </row>
     <row r="25">
@@ -754,13 +627,7 @@
         <v>3</v>
       </c>
       <c r="B25" t="str">
-        <v>4</v>
-      </c>
-      <c r="C25" t="str">
-        <v>일본문화</v>
-      </c>
-      <c r="D25" t="str">
-        <v/>
+        <v>4=일본문화</v>
       </c>
     </row>
     <row r="26">
@@ -768,13 +635,7 @@
         <v>3</v>
       </c>
       <c r="B26" t="str">
-        <v>5</v>
-      </c>
-      <c r="C26" t="str">
-        <v>논술</v>
-      </c>
-      <c r="D26" t="str">
-        <v/>
+        <v>5=논술</v>
       </c>
     </row>
     <row r="27">
@@ -782,13 +643,7 @@
         <v>3</v>
       </c>
       <c r="B27" t="str">
-        <v>5</v>
-      </c>
-      <c r="C27" t="str">
-        <v>일본문화</v>
-      </c>
-      <c r="D27" t="str">
-        <v/>
+        <v>5=일본문화</v>
       </c>
     </row>
     <row r="28">
@@ -796,13 +651,7 @@
         <v>3</v>
       </c>
       <c r="B28" t="str">
-        <v>6</v>
-      </c>
-      <c r="C28" t="str">
-        <v>논술</v>
-      </c>
-      <c r="D28" t="str">
-        <v/>
+        <v>6=논술</v>
       </c>
     </row>
     <row r="29">
@@ -810,13 +659,7 @@
         <v>3</v>
       </c>
       <c r="B29" t="str">
-        <v>6</v>
-      </c>
-      <c r="C29" t="str">
-        <v>인공지능기초</v>
-      </c>
-      <c r="D29" t="str">
-        <v>정보실 전 시수</v>
+        <v>6=물리학Ⅱ, 8=화학Ⅱ, 10=생명과학Ⅱ</v>
       </c>
     </row>
     <row r="30">
@@ -824,13 +667,7 @@
         <v>3</v>
       </c>
       <c r="B30" t="str">
-        <v>6, 7</v>
-      </c>
-      <c r="C30" t="str">
-        <v>지구과학Ⅱ, 화학Ⅱ</v>
-      </c>
-      <c r="D30" t="str">
-        <v>생명과학실 전 시수, -</v>
+        <v>6=인공지능기초</v>
       </c>
     </row>
     <row r="31">
@@ -838,13 +675,7 @@
         <v>3</v>
       </c>
       <c r="B31" t="str">
-        <v>6, 8, 10</v>
-      </c>
-      <c r="C31" t="str">
-        <v>물리학Ⅱ, 화학Ⅱ, 생명과학Ⅱ</v>
-      </c>
-      <c r="D31" t="str">
-        <v/>
+        <v>6=지구과학Ⅱ, 7=화학Ⅱ</v>
       </c>
     </row>
     <row r="32">
@@ -852,13 +683,7 @@
         <v>3</v>
       </c>
       <c r="B32" t="str">
-        <v>7</v>
-      </c>
-      <c r="C32" t="str">
-        <v>물리학Ⅱ</v>
-      </c>
-      <c r="D32" t="str">
-        <v/>
+        <v>7=물리학Ⅱ</v>
       </c>
     </row>
     <row r="33">
@@ -866,13 +691,7 @@
         <v>3</v>
       </c>
       <c r="B33" t="str">
-        <v>7</v>
-      </c>
-      <c r="C33" t="str">
-        <v>인공지능기초</v>
-      </c>
-      <c r="D33" t="str">
-        <v>정보실 전 시수</v>
+        <v>7=인공지능기초</v>
       </c>
     </row>
     <row r="34">
@@ -880,13 +699,7 @@
         <v>3</v>
       </c>
       <c r="B34" t="str">
-        <v>8, 8, 9, 9</v>
-      </c>
-      <c r="C34" t="str">
-        <v>물리학Ⅱ, 수학과제탐구, 논술, 생명과학Ⅱ</v>
-      </c>
-      <c r="D34" t="str">
-        <v/>
+        <v>8=물리학Ⅱ, 8=수학과제탐구, 9=논술, 9=생명과학Ⅱ</v>
       </c>
     </row>
     <row r="35">
@@ -894,13 +707,7 @@
         <v>3</v>
       </c>
       <c r="B35" t="str">
-        <v>9</v>
-      </c>
-      <c r="C35" t="str">
-        <v>인공지능기초</v>
-      </c>
-      <c r="D35" t="str">
-        <v>정보실 전 시수</v>
+        <v>9=인공지능기초</v>
       </c>
     </row>
     <row r="36">
@@ -908,18 +715,12 @@
         <v>3</v>
       </c>
       <c r="B36" t="str">
-        <v>9</v>
-      </c>
-      <c r="C36" t="str">
-        <v>화학Ⅱ</v>
-      </c>
-      <c r="D36" t="str">
-        <v/>
+        <v>9=화학Ⅱ</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D36"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B36"/>
   </ignoredErrors>
 </worksheet>
 </file>